--- a/ig/DM-37/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="160">
   <si>
     <t>Property</t>
   </si>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -198,24 +198,6 @@
     <t>Document de liaison d'urgence</t>
   </si>
   <si>
-    <t>urn:asip:ci-sis:dlu-dlu-dom:2022</t>
-  </si>
-  <si>
-    <t>Document de liaison d'urgence DOM</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:dlu-fludr-dom:2022</t>
-  </si>
-  <si>
-    <t>Fiche de liaison d'urgence - Retour des urgences vers le domicile</t>
-  </si>
-  <si>
-    <t>urn:asip:ci-sis:dlu-fludt-dom:2022</t>
-  </si>
-  <si>
-    <t>Fiche de liaison d'urgence - Transfert du domicile vers les urgences</t>
-  </si>
-  <si>
     <t>urn:asip:ci-sis:eunv:2013</t>
   </si>
   <si>
@@ -390,6 +372,21 @@
     <t>Feuille de style</t>
   </si>
   <si>
+    <t>urn:asip:ci-sis:dlu:2024</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ft-su:2024</t>
+  </si>
+  <si>
+    <t>Fiche de transfert vers le service des urgences</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:fr-su:2024</t>
+  </si>
+  <si>
+    <t>Fiche de retour du service des urgences</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -454,9 +451,6 @@
   </si>
   <si>
     <t>urn:ihe:pcc:ips:2020</t>
-  </si>
-  <si>
-    <t>Synthèse du dossier médical</t>
   </si>
   <si>
     <t>urn:ihe:pharm:pre:2010</t>
@@ -1143,39 +1137,39 @@
         <v>118</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>119</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>121</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>123</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1202,130 +1196,130 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>130</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>132</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>136</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>140</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -1352,26 +1346,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -1398,26 +1392,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-37/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="168">
   <si>
     <t>Property</t>
   </si>
@@ -216,6 +216,24 @@
     <t>Fiche de liaison d'urgence - Transfert de l'EHPAD vers les urgences</t>
   </si>
   <si>
+    <t>urn:asip:ci-sis:dlu-fludr-dom:2022</t>
+  </si>
+  <si>
+    <t>Fiche de liaison d'urgence - Retour des urgences vers le domicile</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-fludt-dom:2022</t>
+  </si>
+  <si>
+    <t>FFiche de liaison d'urgence - Transfert du domicile vers les urgences</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu-dlu-dom:2022</t>
+  </si>
+  <si>
+    <t>Document de liaison d'urgence DOM</t>
+  </si>
+  <si>
     <t>urn:asip:ci-sis:frcp:2011</t>
   </si>
   <si>
@@ -385,6 +403,12 @@
   </si>
   <si>
     <t>Fiche de retour du service des urgences</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:export-dui:2023</t>
+  </si>
+  <si>
+    <t>Export du Dossier Usager informatisé</t>
   </si>
   <si>
     <t/>
@@ -765,7 +789,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1137,39 +1161,71 @@
         <v>118</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>59</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>123</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1196,130 +1252,130 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -1346,26 +1402,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1392,26 +1448,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-37/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="192">
   <si>
     <t>Property</t>
   </si>
@@ -411,6 +411,12 @@
     <t>Export du Dossier Usager informatisé</t>
   </si>
   <si>
+    <t>urn:asip:ci-sis:cva:2017</t>
+  </si>
+  <si>
+    <t>Carnet de vaccination électronique</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -499,6 +505,72 @@
   </si>
   <si>
     <t>Compte-rendu d'imagerie médicale</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:all:2010</t>
+  </si>
+  <si>
+    <t>Compte rendu d'anatomie et de cytologie pathologiques - Modèle générique</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:breast:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:colon:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:prostate:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:thyroid:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:lung:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:skin:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:kidney:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:cervix:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:endometrium:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:ovary:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:esophagus:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:stomach:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:liver:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:pancreas:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:testis:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:urinary_bladder:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:lip_oral_cavity:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:pharynx:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:salivary_gland:2010</t>
+  </si>
+  <si>
+    <t>urn:ihe:pat:apsr:larynx:2010</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
@@ -789,7 +861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1217,15 +1289,23 @@
         <v>131</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>133</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1252,79 +1332,79 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>109</v>
@@ -1332,50 +1412,178 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
+      </c>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -1402,26 +1610,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>163</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>164</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -1448,26 +1656,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>166</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>167</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
